--- a/model/Salesforce_CRM_Model.xlsx
+++ b/model/Salesforce_CRM_Model.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="358">
   <si>
     <t xml:space="preserve">Salesforce, Inc. (NYSE: CRM) - 3-Statement Model &amp; DCF</t>
   </si>
@@ -75,19 +75,19 @@
     <t xml:space="preserve">Active scenario</t>
   </si>
   <si>
-    <t xml:space="preserve">Implied value per share - blended ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implied value per share - perpetuity ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implied value per share - exit multiple ($)</t>
+    <t xml:space="preserve">Value per share - headline: perpetuity growth ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value per share - exit multiple, cross-check ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied perpetuity growth in the exit multiple</t>
   </si>
   <si>
     <t xml:space="preserve">Current share price ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Upside / (downside) - blended</t>
+    <t xml:space="preserve">Upside / (downside) - headline</t>
   </si>
   <si>
     <t xml:space="preserve">WACC</t>
@@ -108,7 +108,10 @@
     <t xml:space="preserve">FY31E non-GAAP operating margin</t>
   </si>
   <si>
-    <t xml:space="preserve">FY31E free cash flow (CFO - capex)</t>
+    <t xml:space="preserve">FY31E free cash flow: CFO - capex (SBC added back, after interest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY31E unlevered FCF valued in the DCF (SBC as a cost, before interest)</t>
   </si>
   <si>
     <t xml:space="preserve">Model integrity checks</t>
@@ -120,12 +123,18 @@
     <t xml:space="preserve">Forecast cash stays positive?</t>
   </si>
   <si>
-    <t xml:space="preserve">Historical CF ties to reported CFO?</t>
-  </si>
-  <si>
     <t xml:space="preserve">WACC &gt; terminal growth?</t>
   </si>
   <si>
+    <t xml:space="preserve">Exit multiple consistent with perpetuity growth (implied g within 1 pt)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Info: largest historical 'other operating' plug, % of reported CFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plug forces the CFO tie; size = what the simplified CF lines don't explain</t>
+  </si>
+  <si>
     <t xml:space="preserve">Scenario snapshot (values pasted at build; re-run by changing Assumptions!B4)</t>
   </si>
   <si>
@@ -138,16 +147,22 @@
     <t xml:space="preserve">Upside</t>
   </si>
   <si>
-    <t xml:space="preserve">Value per share - blended ($)</t>
+    <t xml:space="preserve">Value per share - headline ($)</t>
   </si>
   <si>
     <t xml:space="preserve">Upside / (downside)</t>
   </si>
   <si>
+    <t xml:space="preserve">Value per share - exit multiple ($)</t>
+  </si>
+  <si>
     <t xml:space="preserve">FY31E revenue ($mm)</t>
   </si>
   <si>
-    <t xml:space="preserve">FY31E free cash flow ($mm)</t>
+    <t xml:space="preserve">FY31E FCF: CFO - capex ($mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY31E unlevered FCF in DCF ($mm)</t>
   </si>
   <si>
     <t xml:space="preserve">Snapshot uses base valuation inputs (WACC, terminal growth, exit multiple) in all three scenarios.</t>
@@ -168,7 +183,10 @@
     <t xml:space="preserve">4. Statements: IS -&gt; BS -&gt; CF. Ending cash on CF feeds BS cash; BS!31 must be 0 in every year.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. DCF: B16 toggles whether SBC is treated as a real cost (default 1 = yes). Sensitivity tables at DCF!A80 and A89.</t>
+    <t xml:space="preserve">5. DCF: headline = perpetuity growth; exit multiple is a cross-check (DCF!B35 sets the weight). B16 toggles SBC as a cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Sensitivity tables at DCF!A80 and A89.</t>
   </si>
   <si>
     <t xml:space="preserve">Colour code: blue = hardcoded input, black = formula, green = link to another sheet, yellow = key lever.</t>
@@ -252,22 +270,22 @@
     <t xml:space="preserve">Cost structure (GAAP, SBC embedded in each line)</t>
   </si>
   <si>
-    <t xml:space="preserve">   Cost of sub &amp; support (% of sub rev) - Downside</t>
+    <t xml:space="preserve">   Cost of sub &amp; support excl. amortization (% of sub rev) - Downside</t>
   </si>
   <si>
     <t xml:space="preserve">Downside: AI inference/compute costs pressure gross margin</t>
   </si>
   <si>
-    <t xml:space="preserve">   Cost of sub &amp; support (% of sub rev) - Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical: 20.1% / 19.0% / 17.4% / 17.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Cost of sub &amp; support (% of sub rev) - Upside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Cost of sub &amp; support (% of sub rev) - LIVE</t>
+    <t xml:space="preserve">   Cost of sub &amp; support excl. amortization (% of sub rev) - Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excl. acquired-intangible amortization: FY25 15.3%, FY26 15.5% (incl.: 17.4% / 17.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Cost of sub &amp; support excl. amortization (% of sub rev) - Upside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Cost of sub &amp; support excl. amortization - LIVE</t>
   </si>
   <si>
     <t xml:space="preserve">   Cost of prof. services (% of PS rev)</t>
@@ -282,19 +300,19 @@
     <t xml:space="preserve">Historical: 16.1% / 14.1% / 14.5% / 14.4%; FY27 adds Informatica R&amp;D</t>
   </si>
   <si>
-    <t xml:space="preserve">   Sales &amp; marketing (% of revenue) - Downside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Sales &amp; marketing (% of revenue) - Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical: 43.1% / 36.9% / 35.0% / 34.5%. Base = ~50bp/yr efficiency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Sales &amp; marketing (% of revenue) - Upside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Sales &amp; marketing (% of revenue) - LIVE</t>
+    <t xml:space="preserve">   Sales &amp; marketing excl. amortization (% of revenue) - Downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Sales &amp; marketing excl. amortization (% of revenue) - Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excl. amortization: FY25 32.6%, FY26 32.2% (incl.: 35.0% / 34.5%). Base = ~50bp/yr efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Sales &amp; marketing excl. amortization (% of revenue) - Upside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Sales &amp; marketing excl. amortization - LIVE</t>
   </si>
   <si>
     <t xml:space="preserve">   G&amp;A (% of revenue)</t>
@@ -318,13 +336,13 @@
     <t xml:space="preserve">   Amortization of acquired intangibles ($mm)</t>
   </si>
   <si>
-    <t xml:space="preserve">FY26 $1,687mm; Informatica adds a full year in FY27, then roll-off. Capped at remaining balance</t>
+    <t xml:space="preserve">FY26 $1,687mm; Informatica adds a full year in FY27, then roll-off. Capped at remaining balance. Added to cost of revenue and S&amp;M on the IS, so the roll-off lifts GAAP EBIT</t>
   </si>
   <si>
     <t xml:space="preserve">   Depreciation (% of beginning PP&amp;E)</t>
   </si>
   <si>
-    <t xml:space="preserve">Owned PP&amp;E only. Finance-lease depreciation and lease principal payments are excluded (roughly offset)</t>
+    <t xml:space="preserve">Owned PP&amp;E only. Finance-lease costs stay inside the % of revenue cost lines as if paid in cash, instead of non-cash depreciation plus financing-line principal payments</t>
   </si>
   <si>
     <t xml:space="preserve">   Capex (% of revenue)</t>
@@ -441,6 +459,12 @@
     <t xml:space="preserve">Net of SBC dilution and buybacks</t>
   </si>
   <si>
+    <t xml:space="preserve">   Share of intangible amortization booked in cost of revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY26: $692mm of $1,687mm in cost of revenue; remainder in sales &amp; marketing</t>
+  </si>
+  <si>
     <t xml:space="preserve">Salesforce - RPO-Driven Revenue Build</t>
   </si>
   <si>
@@ -861,7 +885,7 @@
     <t xml:space="preserve">   Risk-free rate (10Y UST)</t>
   </si>
   <si>
-    <t xml:space="preserve">10Y Treasury ~5.19-5.24%, Oct 9-13, 2026</t>
+    <t xml:space="preserve">FRED DGS10: 5.21% on Oct 13, 2026 (latest close before valuation date)</t>
   </si>
   <si>
     <t xml:space="preserve">   Equity risk premium</t>
@@ -873,7 +897,7 @@
     <t xml:space="preserve">   Levered beta</t>
   </si>
   <si>
-    <t xml:space="preserve">5Y monthly beta, stockanalysis.com</t>
+    <t xml:space="preserve">Yahoo Finance 'Beta (5Y monthly)' 1.26 vs S&amp;P 500; stockanalysis.com 'Beta (5Y)' 1.26</t>
   </si>
   <si>
     <t xml:space="preserve">Cost of equity (CAPM)</t>
@@ -918,10 +942,13 @@
     <t xml:space="preserve">   Exit EV / EBITDA multiple (on FY31 GAAP EBITDA)</t>
   </si>
   <si>
-    <t xml:space="preserve">CRM trades ~17-18x FY27E GAAP EBITDA today; assume some compression by FY31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Weight on perpetuity method in blended value</t>
+    <t xml:space="preserve">GAAP EBITDA (SBC as a cost). 13x GAAP ~ 10x adj. EBITDA. Chosen so implied growth (B64) stays close to B33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Weight on perpetuity method in headline value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headline = perpetuity growth (consistent with SBC-as-cost UFCF). Exit multiple is a cross-check; set 50% to blend</t>
   </si>
   <si>
     <t xml:space="preserve">Unlevered free cash flow ($mm)</t>
@@ -1014,7 +1041,7 @@
     <t xml:space="preserve">Exit multiple</t>
   </si>
   <si>
-    <t xml:space="preserve">Blended</t>
+    <t xml:space="preserve">Headline</t>
   </si>
   <si>
     <t xml:space="preserve">Enterprise value</t>
@@ -1080,16 +1107,22 @@
     <t xml:space="preserve">Salesforce Q2 FY27 earnings release (Aug 26, 2026): https://investor.salesforce.com/files/doc_financials/2027/q2/CRM-Q2-FY27-Earnings-Press-Release.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Share price, shares outstanding, beta</t>
+    <t xml:space="preserve">Share price, shares outstanding</t>
   </si>
   <si>
     <t xml:space="preserve">stockanalysis.com/stocks/crm (close Oct 14, 2026)</t>
   </si>
   <si>
+    <t xml:space="preserve">Beta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yahoo Finance 'Beta (5Y monthly)' = 1.26 (monthly returns vs S&amp;P 500, 5 years); cross-checked with stockanalysis.com 'Beta (5Y)' = 1.26 (S&amp;P Global data)</t>
+  </si>
+  <si>
     <t xml:space="preserve">10-year Treasury yield</t>
   </si>
   <si>
-    <t xml:space="preserve">themortgagereports.com (Oct 13, 2026: 5.19%); etfdb.com (Oct 9, 2026: 5.24%)</t>
+    <t xml:space="preserve">FRED series DGS10 (Board of Governors via St. Louis Fed): 5.21% on Oct 13, 2026. https://fred.stlouisfed.org/series/DGS10</t>
   </si>
   <si>
     <t xml:space="preserve">Combined balance sheet lines</t>
@@ -1352,6 +1385,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1393,10 +1430,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1760,7 +1793,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -1814,7 +1847,7 @@
       </c>
       <c r="B6" s="8" t="n">
         <f aca="false">DCF!D74</f>
-        <v>230.364412252662</v>
+        <v>221.760297657315</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1824,8 +1857,8 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="n">
-        <f aca="false">DCF!B74</f>
-        <v>199.124756574782</v>
+        <f aca="false">DCF!C74</f>
+        <v>245.307081437119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1834,9 +1867,9 @@
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="n">
-        <f aca="false">DCF!C74</f>
-        <v>261.604067930543</v>
+      <c r="B8" s="9" t="n">
+        <f aca="false">DCF!B64</f>
+        <v>0.0378177373640239</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1858,7 +1891,7 @@
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">DCF!D76</f>
-        <v>-0.0236727601073857</v>
+        <v>-0.0601385986127792</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1869,7 +1902,7 @@
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">DCF!B30</f>
-        <v>0.103044493496054</v>
+        <v>0.103127784192764</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1916,7 +1949,7 @@
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">IS!J22</f>
-        <v>0.24890527262271</v>
+        <v>0.282218685781069</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -1927,7 +1960,7 @@
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">IS!J44</f>
-        <v>0.344587595126811</v>
+        <v>0.377901008285169</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1938,42 +1971,42 @@
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">CF!J32</f>
-        <v>20151.7579046945</v>
+        <v>21933.8385232629</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="A18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="10" t="n">
+        <f aca="false">DCF!J47</f>
+        <v>16508.7666742267</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="11" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(BS!D31:J31))&lt;0.01,"OK","ERROR")</f>
-        <v>OK</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="11" t="str">
-        <f aca="false">IF(MIN(BS!F5:J5)&gt;0,"OK","NEGATIVE CASH")</f>
+        <f aca="false">IF(SUMPRODUCT(ABS(BS!D31:J31))&lt;0.01,"OK","ERROR")</f>
         <v>OK</v>
       </c>
       <c r="C21" s="2"/>
@@ -1984,7 +2017,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="11" t="str">
-        <f aca="false">IF(SUMPRODUCT(ABS(CF!B14:E14-CF!B15:E15))&lt;0.01,"OK","ERROR")</f>
+        <f aca="false">IF(MIN(BS!F5:J5)&gt;0,"OK","NEGATIVE CASH")</f>
         <v>OK</v>
       </c>
       <c r="C22" s="2"/>
@@ -2002,158 +2035,178 @@
       <c r="D23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="A24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="11" t="str">
+        <f aca="false">IF(ABS(DCF!B64-DCF!B33)&lt;=0.01,"OK","CHECK")</f>
+        <v>OK</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="A25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="12" t="n">
+        <f aca="false">MAX(ABS(CF!B13/CF!B15),ABS(CF!C13/CF!C15),ABS(CF!D13/CF!D15),ABS(CF!E13/CF!E15))</f>
+        <v>0.26803543805372</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
-      <c r="B26" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="12" t="s">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="13" t="n">
-        <v>179.9113</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>230.3644</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>265.0172</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="C28" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>-0.2375</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>-0.0237</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>0.1232</v>
+      <c r="D28" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>58522.1</v>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>67037</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>72624.8</v>
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>171.48</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>221.76</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>255.81</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>0.2241</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>0.2489</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>0.2642</v>
+        <v>29</v>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>-0.2733</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>-0.0601</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0.0842</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>15916.5</v>
-      </c>
-      <c r="C31" s="15" t="n">
-        <v>20151.8</v>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>23023.8</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>195.58</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>245.31</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>279.56</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="A32" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="16" t="n">
+        <v>58522.14</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>67037.02</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>72624.8</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="A33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>0.298</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+      <c r="A34" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>17421.17</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>21933.84</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>24985.56</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>12818.23</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>16508.77</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>19022.26</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>32</v>
+      <c r="A36" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="A38" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2161,11 +2214,51 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2183,7 +2276,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -2193,7 +2286,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2208,7 +2301,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2235,10 +2328,10 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="11" t="str">
@@ -2269,29 +2362,29 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2321,122 +2414,122 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
+      <c r="A9" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <v>0.09</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="23" t="n">
         <v>0.07</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="23" t="n">
         <v>0.06</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="23" t="n">
         <v>0.045</v>
       </c>
       <c r="K10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="23" t="n">
         <v>0.12</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="23" t="n">
         <v>0.105</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="23" t="n">
         <v>0.09</v>
       </c>
-      <c r="J11" s="22" t="n">
+      <c r="J11" s="23" t="n">
         <v>0.08</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>0.14</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="23" t="n">
         <v>0.13</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="23" t="n">
         <v>0.12</v>
       </c>
-      <c r="I12" s="22" t="n">
+      <c r="I12" s="23" t="n">
         <v>0.11</v>
       </c>
-      <c r="J12" s="22" t="n">
+      <c r="J12" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="K12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>52</v>
+      <c r="A13" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="12" t="n">
         <f aca="false">CHOOSE($B$4,F10,F11,F12)</f>
         <v>0.12</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="12" t="n">
         <f aca="false">CHOOSE($B$4,G10,G11,G12)</f>
         <v>0.105</v>
       </c>
-      <c r="H13" s="23" t="n">
+      <c r="H13" s="12" t="n">
         <f aca="false">CHOOSE($B$4,H10,H11,H12)</f>
         <v>0.1</v>
       </c>
-      <c r="I13" s="23" t="n">
+      <c r="I13" s="12" t="n">
         <f aca="false">CHOOSE($B$4,I10,I11,I12)</f>
         <v>0.09</v>
       </c>
-      <c r="J13" s="23" t="n">
+      <c r="J13" s="12" t="n">
         <f aca="false">CHOOSE($B$4,J10,J11,J12)</f>
         <v>0.08</v>
       </c>
@@ -2444,7 +2537,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2466,12 +2559,12 @@
         <v>1.25</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2493,12 +2586,12 @@
         <v>0.485</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2523,7 +2616,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2545,12 +2638,12 @@
         <v>-0.02</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2574,30 +2667,30 @@
       <c r="K18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>61</v>
+      <c r="A19" s="18" t="s">
+        <v>67</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="23" t="n">
+      <c r="F19" s="12" t="n">
         <f aca="false">CHOOSE($B$4,F16,F17,F18)</f>
         <v>-0.02</v>
       </c>
-      <c r="G19" s="23" t="n">
+      <c r="G19" s="12" t="n">
         <f aca="false">CHOOSE($B$4,G16,G17,G18)</f>
         <v>-0.02</v>
       </c>
-      <c r="H19" s="23" t="n">
+      <c r="H19" s="12" t="n">
         <f aca="false">CHOOSE($B$4,H16,H17,H18)</f>
         <v>-0.02</v>
       </c>
-      <c r="I19" s="23" t="n">
+      <c r="I19" s="12" t="n">
         <f aca="false">CHOOSE($B$4,I16,I17,I18)</f>
         <v>-0.02</v>
       </c>
-      <c r="J19" s="23" t="n">
+      <c r="J19" s="12" t="n">
         <f aca="false">CHOOSE($B$4,J16,J17,J18)</f>
         <v>-0.02</v>
       </c>
@@ -2617,132 +2710,132 @@
       <c r="K20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
+      <c r="A21" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
       <c r="K21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="25" t="n">
-        <v>0.185</v>
+        <v>0.1675</v>
       </c>
       <c r="G22" s="25" t="n">
-        <v>0.185</v>
+        <v>0.1675</v>
       </c>
       <c r="H22" s="25" t="n">
-        <v>0.185</v>
+        <v>0.1675</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>0.185</v>
+        <v>0.1675</v>
       </c>
       <c r="J22" s="25" t="n">
-        <v>0.185</v>
+        <v>0.1675</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="25" t="n">
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="J23" s="25" t="n">
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="25" t="n">
-        <v>0.17</v>
+        <v>0.1525</v>
       </c>
       <c r="G24" s="25" t="n">
-        <v>0.17</v>
+        <v>0.1525</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>0.17</v>
+        <v>0.1525</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>0.17</v>
+        <v>0.1525</v>
       </c>
       <c r="J24" s="25" t="n">
-        <v>0.17</v>
+        <v>0.1525</v>
       </c>
       <c r="K24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>68</v>
+      <c r="A25" s="18" t="s">
+        <v>74</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="23" t="n">
+      <c r="F25" s="12" t="n">
         <f aca="false">CHOOSE($B$4,F22,F23,F24)</f>
-        <v>0.175</v>
-      </c>
-      <c r="G25" s="23" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <f aca="false">CHOOSE($B$4,G22,G23,G24)</f>
-        <v>0.175</v>
-      </c>
-      <c r="H25" s="23" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <f aca="false">CHOOSE($B$4,H22,H23,H24)</f>
-        <v>0.175</v>
-      </c>
-      <c r="I25" s="23" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="I25" s="12" t="n">
         <f aca="false">CHOOSE($B$4,I22,I23,I24)</f>
-        <v>0.175</v>
-      </c>
-      <c r="J25" s="23" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="J25" s="12" t="n">
         <f aca="false">CHOOSE($B$4,J22,J23,J24)</f>
-        <v>0.175</v>
+        <v>0.1575</v>
       </c>
       <c r="K25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2764,12 +2857,12 @@
         <v>1.15</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2791,119 +2884,119 @@
         <v>0.148</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="22" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="G28" s="22" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="H28" s="22" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="J28" s="22" t="n">
-        <v>0.342</v>
+      <c r="F28" s="23" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="G28" s="23" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="H28" s="23" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>0.318</v>
       </c>
       <c r="K28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="22" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="G29" s="22" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H29" s="22" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J29" s="22" t="n">
-        <v>0.325</v>
+      <c r="F29" s="23" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="G29" s="23" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="H29" s="23" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="I29" s="23" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="J29" s="23" t="n">
+        <v>0.301</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="22" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="G30" s="22" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="H30" s="22" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="I30" s="22" t="n">
+      <c r="F30" s="23" t="n">
         <v>0.319</v>
       </c>
-      <c r="J30" s="22" t="n">
+      <c r="G30" s="23" t="n">
         <v>0.311</v>
       </c>
+      <c r="H30" s="23" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="J30" s="23" t="n">
+        <v>0.287</v>
+      </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
-        <v>77</v>
+      <c r="A31" s="18" t="s">
+        <v>83</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="23" t="n">
+      <c r="F31" s="12" t="n">
         <f aca="false">CHOOSE($B$4,F28,F29,F30)</f>
-        <v>0.345</v>
-      </c>
-      <c r="G31" s="23" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="G31" s="12" t="n">
         <f aca="false">CHOOSE($B$4,G28,G29,G30)</f>
-        <v>0.34</v>
-      </c>
-      <c r="H31" s="23" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="H31" s="12" t="n">
         <f aca="false">CHOOSE($B$4,H28,H29,H30)</f>
-        <v>0.335</v>
-      </c>
-      <c r="I31" s="23" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="I31" s="12" t="n">
         <f aca="false">CHOOSE($B$4,I28,I29,I30)</f>
-        <v>0.33</v>
-      </c>
-      <c r="J31" s="23" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <f aca="false">CHOOSE($B$4,J28,J29,J30)</f>
-        <v>0.325</v>
+        <v>0.301</v>
       </c>
       <c r="K31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2925,12 +3018,12 @@
         <v>0.07</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2952,12 +3045,12 @@
         <v>0.005</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2979,12 +3072,12 @@
         <v>0.083</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3006,12 +3099,12 @@
         <v>900</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3033,12 +3126,12 @@
         <v>0.2</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3060,12 +3153,12 @@
         <v>0.015</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3087,12 +3180,12 @@
         <v>0.215</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -3114,12 +3207,12 @@
         <v>0.045</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3156,23 +3249,23 @@
       <c r="K41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
+      <c r="A42" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
       <c r="K42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3194,12 +3287,12 @@
         <v>126</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3221,12 +3314,12 @@
         <v>0.122</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3248,12 +3341,12 @@
         <v>0.054</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3275,34 +3368,34 @@
         <v>0.199</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="22" t="n">
+      <c r="F47" s="23" t="n">
         <v>0.585</v>
       </c>
-      <c r="G47" s="22" t="n">
+      <c r="G47" s="23" t="n">
         <v>0.585</v>
       </c>
-      <c r="H47" s="22" t="n">
+      <c r="H47" s="23" t="n">
         <v>0.585</v>
       </c>
-      <c r="I47" s="22" t="n">
+      <c r="I47" s="23" t="n">
         <v>0.585</v>
       </c>
-      <c r="J47" s="22" t="n">
+      <c r="J47" s="23" t="n">
         <v>0.585</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3319,23 +3412,23 @@
       <c r="K48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
+      <c r="A49" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
       <c r="K49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3357,12 +3450,12 @@
         <v>0</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3384,12 +3477,12 @@
         <v>0</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3411,12 +3504,12 @@
         <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3430,12 +3523,12 @@
       <c r="I53" s="26"/>
       <c r="J53" s="26"/>
       <c r="K53" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3455,12 +3548,12 @@
         <v>0.5</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3474,12 +3567,12 @@
       <c r="I55" s="26"/>
       <c r="J55" s="26"/>
       <c r="K55" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3502,7 +3595,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3524,12 +3617,12 @@
         <v>1000</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3543,12 +3636,12 @@
       <c r="I58" s="26"/>
       <c r="J58" s="26"/>
       <c r="K58" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3568,7 +3661,34 @@
         <v>-0.015</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G60" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H60" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I60" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J60" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3596,7 +3716,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3610,7 +3730,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3636,34 +3756,34 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3679,22 +3799,22 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
+      <c r="A6" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B7" s="26" t="n">
         <v>24600</v>
@@ -3731,7 +3851,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="28" t="n">
@@ -3769,7 +3889,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B9" s="26" t="n">
         <v>48600</v>
@@ -3806,7 +3926,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B10" s="28" t="n">
         <f aca="false">B7/B9</f>
@@ -3858,22 +3978,22 @@
       <c r="J11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
+      <c r="A12" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B13" s="26" t="n">
         <v>29021</v>
@@ -3910,7 +4030,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="28" t="n">
@@ -3948,7 +4068,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="29" t="n">
@@ -3986,7 +4106,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B16" s="26" t="n">
         <v>2331</v>
@@ -4023,7 +4143,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="28" t="n">
@@ -4060,8 +4180,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
-        <v>142</v>
+      <c r="A18" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="B18" s="30" t="n">
         <f aca="false">B13+B16</f>
@@ -4102,7 +4222,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="28" t="n">
@@ -4140,7 +4260,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B20" s="28" t="n">
         <f aca="false">B13/B18</f>
@@ -4192,22 +4312,22 @@
       <c r="J21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
+      <c r="A22" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B23" s="26" t="n">
         <v>17376</v>
@@ -4244,7 +4364,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="27" t="n">
@@ -4282,7 +4402,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4328,22 +4448,22 @@
       <c r="J26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
+      <c r="A27" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B28" s="26" t="n">
         <v>46100</v>
@@ -4361,7 +4481,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B29" s="11" t="str">
         <f aca="false">IF(AND(F18&gt;=B28,F18&lt;=C28),"YES","OUTSIDE")</f>
@@ -4403,7 +4523,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4418,7 +4538,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4446,40 +4566,40 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="K4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B5" s="31" t="n">
         <f aca="false">'Revenue Build'!B13</f>
@@ -4521,7 +4641,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B6" s="31" t="n">
         <f aca="false">'Revenue Build'!B16</f>
@@ -4562,8 +4682,8 @@
       <c r="K6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>142</v>
+      <c r="A7" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="B7" s="30" t="n">
         <f aca="false">B5+B6</f>
@@ -4605,7 +4725,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="28" t="n">
@@ -4657,7 +4777,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>5821</v>
@@ -4672,30 +4792,30 @@
         <v>6796</v>
       </c>
       <c r="F10" s="27" t="n">
-        <f aca="false">F5*Assumptions!F25</f>
-        <v>7721.1225</v>
+        <f aca="false">F5*Assumptions!F25+F39*Assumptions!F60</f>
+        <v>7728.01025</v>
       </c>
       <c r="G10" s="27" t="n">
-        <f aca="false">G5*Assumptions!G25</f>
-        <v>8633.898</v>
+        <f aca="false">G5*Assumptions!G25+G39*Assumptions!G60</f>
+        <v>8467.5082</v>
       </c>
       <c r="H10" s="27" t="n">
-        <f aca="false">H5*Assumptions!H25</f>
-        <v>9502.4475</v>
+        <f aca="false">H5*Assumptions!H25+H39*Assumptions!H60</f>
+        <v>9167.20275</v>
       </c>
       <c r="I10" s="27" t="n">
-        <f aca="false">I5*Assumptions!I25</f>
-        <v>10452.69225</v>
+        <f aca="false">I5*Assumptions!I25+I39*Assumptions!I60</f>
+        <v>9899.423025</v>
       </c>
       <c r="J10" s="27" t="n">
-        <f aca="false">J5*Assumptions!J25</f>
-        <v>11393.4345525</v>
+        <f aca="false">J5*Assumptions!J25+J39*Assumptions!J60</f>
+        <v>10465.24109725</v>
       </c>
       <c r="K10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>2539</v>
@@ -4733,7 +4853,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B12" s="27" t="n">
         <f aca="false">B10+B11</f>
@@ -4753,29 +4873,29 @@
       </c>
       <c r="F12" s="27" t="n">
         <f aca="false">F10+F11</f>
-        <v>10129.5215</v>
+        <v>10136.40925</v>
       </c>
       <c r="G12" s="27" t="n">
         <f aca="false">G10+G11</f>
-        <v>10994.12902</v>
+        <v>10827.73922</v>
       </c>
       <c r="H12" s="27" t="n">
         <f aca="false">H10+H11</f>
-        <v>11815.4738996</v>
+        <v>11480.2291496</v>
       </c>
       <c r="I12" s="27" t="n">
         <f aca="false">I10+I11</f>
-        <v>12719.458121608</v>
+        <v>12166.188896608</v>
       </c>
       <c r="J12" s="27" t="n">
         <f aca="false">J10+J11</f>
-        <v>13614.8651066758</v>
+        <v>12686.6716514258</v>
       </c>
       <c r="K12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>156</v>
+      <c r="A13" s="18" t="s">
+        <v>164</v>
       </c>
       <c r="B13" s="30" t="n">
         <f aca="false">B7-B12</f>
@@ -4795,29 +4915,29 @@
       </c>
       <c r="F13" s="30" t="n">
         <f aca="false">F7-F12</f>
-        <v>36085.4385</v>
+        <v>36078.55075</v>
       </c>
       <c r="G13" s="30" t="n">
         <f aca="false">G7-G12</f>
-        <v>40394.80578</v>
+        <v>40561.19558</v>
       </c>
       <c r="H13" s="30" t="n">
         <f aca="false">H7-H12</f>
-        <v>44495.5534044</v>
+        <v>44830.7981544</v>
       </c>
       <c r="I13" s="30" t="n">
         <f aca="false">I7-I12</f>
-        <v>48981.312636312</v>
+        <v>49534.581861312</v>
       </c>
       <c r="J13" s="30" t="n">
         <f aca="false">J7-J12</f>
-        <v>53422.1539360858</v>
+        <v>54350.3473913358</v>
       </c>
       <c r="K13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B14" s="28" t="n">
         <f aca="false">B13/B7</f>
@@ -4837,23 +4957,23 @@
       </c>
       <c r="F14" s="28" t="n">
         <f aca="false">F13/F7</f>
-        <v>0.780817261337022</v>
+        <v>0.780668224098863</v>
       </c>
       <c r="G14" s="28" t="n">
         <f aca="false">G13/G7</f>
-        <v>0.786060383178053</v>
+        <v>0.789298235852906</v>
       </c>
       <c r="H14" s="28" t="n">
         <f aca="false">H13/H7</f>
-        <v>0.790174776321996</v>
+        <v>0.796128223915664</v>
       </c>
       <c r="I14" s="28" t="n">
         <f aca="false">I13/I7</f>
-        <v>0.793852524606019</v>
+        <v>0.802819498895055</v>
       </c>
       <c r="J14" s="28" t="n">
         <f aca="false">J13/J7</f>
-        <v>0.79690527262271</v>
+        <v>0.810751256058488</v>
       </c>
       <c r="K14" s="2"/>
     </row>
@@ -4872,7 +4992,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B16" s="26" t="n">
         <v>5055</v>
@@ -4910,7 +5030,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B17" s="26" t="n">
         <v>13526</v>
@@ -4925,30 +5045,30 @@
         <v>14345</v>
       </c>
       <c r="F17" s="27" t="n">
-        <f aca="false">F7*Assumptions!F31</f>
-        <v>15944.1612</v>
+        <f aca="false">F7*Assumptions!F31+F39*(1-Assumptions!F60)</f>
+        <v>15956.00216</v>
       </c>
       <c r="G17" s="27" t="n">
-        <f aca="false">G7*Assumptions!G31</f>
-        <v>17472.237832</v>
+        <f aca="false">G7*Assumptions!G31+G39*(1-Assumptions!G60)</f>
+        <v>17241.9033968</v>
       </c>
       <c r="H17" s="27" t="n">
-        <f aca="false">H7*Assumptions!H31</f>
-        <v>18864.19414684</v>
+        <f aca="false">H7*Assumptions!H31+H39*(1-Assumptions!H60)</f>
+        <v>18397.729491544</v>
       </c>
       <c r="I17" s="27" t="n">
-        <f aca="false">I7*Assumptions!I31</f>
-        <v>20361.2543501136</v>
+        <f aca="false">I7*Assumptions!I31+I39*(1-Assumptions!I60)</f>
+        <v>19588.4358519235</v>
       </c>
       <c r="J17" s="27" t="n">
-        <f aca="false">J7*Assumptions!J31</f>
-        <v>21787.0311888975</v>
+        <f aca="false">J7*Assumptions!J31+J39*(1-Assumptions!J60)</f>
+        <v>20481.9927318712</v>
       </c>
       <c r="K17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B18" s="26" t="n">
         <v>2553</v>
@@ -4986,7 +5106,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B19" s="26" t="n">
         <v>828</v>
@@ -5024,7 +5144,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B20" s="27" t="n">
         <f aca="false">SUM(B16:B19)</f>
@@ -5044,29 +5164,29 @@
       </c>
       <c r="F20" s="27" t="n">
         <f aca="false">SUM(F16:F19)</f>
-        <v>26666.03192</v>
+        <v>26677.87288</v>
       </c>
       <c r="G20" s="27" t="n">
         <f aca="false">SUM(G16:G19)</f>
-        <v>29086.1370968</v>
+        <v>28855.8026616</v>
       </c>
       <c r="H20" s="27" t="n">
         <f aca="false">SUM(H16:H19)</f>
-        <v>31534.17529024</v>
+        <v>31067.710634944</v>
       </c>
       <c r="I20" s="27" t="n">
         <f aca="false">SUM(I16:I19)</f>
-        <v>34182.2269998877</v>
+        <v>33409.4085016976</v>
       </c>
       <c r="J20" s="27" t="n">
         <f aca="false">SUM(J16:J19)</f>
-        <v>36736.2864354334</v>
+        <v>35431.2479784071</v>
       </c>
       <c r="K20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
-        <v>163</v>
+      <c r="A21" s="18" t="s">
+        <v>171</v>
       </c>
       <c r="B21" s="30" t="n">
         <f aca="false">B13-B20</f>
@@ -5086,29 +5206,29 @@
       </c>
       <c r="F21" s="30" t="n">
         <f aca="false">F13-F20</f>
-        <v>9419.40658000001</v>
+        <v>9400.67787</v>
       </c>
       <c r="G21" s="30" t="n">
         <f aca="false">G13-G20</f>
-        <v>11308.6686832</v>
+        <v>11705.3929184</v>
       </c>
       <c r="H21" s="30" t="n">
         <f aca="false">H13-H20</f>
-        <v>12961.37811416</v>
+        <v>13763.087519456</v>
       </c>
       <c r="I21" s="30" t="n">
         <f aca="false">I13-I20</f>
-        <v>14799.0856364243</v>
+        <v>16125.1733596144</v>
       </c>
       <c r="J21" s="30" t="n">
         <f aca="false">J13-J20</f>
-        <v>16685.8675006524</v>
+        <v>18919.0994129287</v>
       </c>
       <c r="K21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">B21/B7</f>
@@ -5128,23 +5248,23 @@
       </c>
       <c r="F22" s="28" t="n">
         <f aca="false">F21/F7</f>
-        <v>0.203817261337022</v>
+        <v>0.203412009228181</v>
       </c>
       <c r="G22" s="28" t="n">
         <f aca="false">G21/G7</f>
-        <v>0.220060383178053</v>
+        <v>0.227780415452394</v>
       </c>
       <c r="H22" s="28" t="n">
         <f aca="false">H21/H7</f>
-        <v>0.230174776321996</v>
+        <v>0.244411941646079</v>
       </c>
       <c r="I22" s="28" t="n">
         <f aca="false">I21/I7</f>
-        <v>0.239852524606019</v>
+        <v>0.261344763793644</v>
       </c>
       <c r="J22" s="28" t="n">
         <f aca="false">J21/J7</f>
-        <v>0.24890527262271</v>
+        <v>0.282218685781069</v>
       </c>
       <c r="K22" s="2"/>
     </row>
@@ -5163,7 +5283,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B24" s="26" t="n">
         <v>-239</v>
@@ -5198,12 +5318,12 @@
         <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -5215,25 +5335,25 @@
       </c>
       <c r="G25" s="27" t="n">
         <f aca="false">Assumptions!G40*(BS!F5+BS!F6)</f>
-        <v>673.690302581343</v>
+        <v>673.144594793718</v>
       </c>
       <c r="H25" s="27" t="n">
         <f aca="false">Assumptions!H40*(BS!G5+BS!G6)</f>
-        <v>938.112836683808</v>
+        <v>943.398381596534</v>
       </c>
       <c r="I25" s="27" t="n">
         <f aca="false">Assumptions!I40*(BS!H5+BS!H6)</f>
-        <v>1229.62265998692</v>
+        <v>1246.78616182303</v>
       </c>
       <c r="J25" s="27" t="n">
         <f aca="false">Assumptions!J40*(BS!I5+BS!I6)</f>
-        <v>1553.63952363759</v>
+        <v>1590.57400444206</v>
       </c>
       <c r="K25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -5263,7 +5383,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B27" s="26" t="n">
         <v>-131</v>
@@ -5283,25 +5403,25 @@
       </c>
       <c r="G27" s="27" t="n">
         <f aca="false">G25+G26</f>
-        <v>-1093.95469741866</v>
+        <v>-1094.50040520628</v>
       </c>
       <c r="H27" s="27" t="n">
         <f aca="false">H25+H26</f>
-        <v>-829.532163316192</v>
+        <v>-824.246618403466</v>
       </c>
       <c r="I27" s="27" t="n">
         <f aca="false">I25+I26</f>
-        <v>-538.022340013085</v>
+        <v>-520.858838176974</v>
       </c>
       <c r="J27" s="27" t="n">
         <f aca="false">J25+J26</f>
-        <v>-214.005476362409</v>
+        <v>-177.070995557944</v>
       </c>
       <c r="K27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>170</v>
+      <c r="A28" s="18" t="s">
+        <v>178</v>
       </c>
       <c r="B28" s="30" t="n">
         <f aca="false">B21+B24+B27</f>
@@ -5321,29 +5441,29 @@
       </c>
       <c r="F28" s="30" t="n">
         <f aca="false">F21+F24+F27</f>
-        <v>8569.39408000001</v>
+        <v>8550.66537</v>
       </c>
       <c r="G28" s="30" t="n">
         <f aca="false">G21+G24+G27</f>
-        <v>10214.7139857813</v>
+        <v>10610.8925131937</v>
       </c>
       <c r="H28" s="30" t="n">
         <f aca="false">H21+H24+H27</f>
-        <v>12131.8459508438</v>
+        <v>12938.8409010525</v>
       </c>
       <c r="I28" s="30" t="n">
         <f aca="false">I21+I24+I27</f>
-        <v>14261.0632964112</v>
+        <v>15604.3145214374</v>
       </c>
       <c r="J28" s="30" t="n">
         <f aca="false">J21+J24+J27</f>
-        <v>16471.86202429</v>
+        <v>18742.0284173707</v>
       </c>
       <c r="K28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B29" s="26" t="n">
         <v>-452</v>
@@ -5359,29 +5479,29 @@
       </c>
       <c r="F29" s="27" t="n">
         <f aca="false">-F28*Assumptions!F38</f>
-        <v>-1910.97487984</v>
+        <v>-1906.79837751</v>
       </c>
       <c r="G29" s="27" t="n">
         <f aca="false">-G28*Assumptions!G38</f>
-        <v>-2196.16350694299</v>
+        <v>-2281.34189033665</v>
       </c>
       <c r="H29" s="27" t="n">
         <f aca="false">-H28*Assumptions!H38</f>
-        <v>-2608.34687943142</v>
+        <v>-2781.8507937263</v>
       </c>
       <c r="I29" s="27" t="n">
         <f aca="false">-I28*Assumptions!I38</f>
-        <v>-3066.12860872842</v>
+        <v>-3354.92762210905</v>
       </c>
       <c r="J29" s="27" t="n">
         <f aca="false">-J28*Assumptions!J38</f>
-        <v>-3541.45033522235</v>
+        <v>-4029.53610973471</v>
       </c>
       <c r="K29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
-        <v>172</v>
+      <c r="A30" s="18" t="s">
+        <v>180</v>
       </c>
       <c r="B30" s="30" t="n">
         <f aca="false">B28+B29</f>
@@ -5401,29 +5521,29 @@
       </c>
       <c r="F30" s="30" t="n">
         <f aca="false">F28+F29</f>
-        <v>6658.41920016</v>
+        <v>6643.86699249</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">G28+G29</f>
-        <v>8018.55047883836</v>
+        <v>8329.55062285707</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">H28+H29</f>
-        <v>9523.49907141239</v>
+        <v>10156.9901073262</v>
       </c>
       <c r="I30" s="30" t="n">
         <f aca="false">I28+I29</f>
-        <v>11194.9346876828</v>
+        <v>12249.3868993284</v>
       </c>
       <c r="J30" s="30" t="n">
         <f aca="false">J28+J29</f>
-        <v>12930.4116890676</v>
+        <v>14712.492307636</v>
       </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B31" s="28" t="n">
         <f aca="false">B30/B7</f>
@@ -5443,29 +5563,29 @@
       </c>
       <c r="F31" s="28" t="n">
         <f aca="false">F30/F7</f>
-        <v>0.144074974860089</v>
+        <v>0.143760093971519</v>
       </c>
       <c r="G31" s="28" t="n">
         <f aca="false">G30/G7</f>
-        <v>0.156036518562715</v>
+        <v>0.162088407850343</v>
       </c>
       <c r="H31" s="28" t="n">
         <f aca="false">H30/H7</f>
-        <v>0.169123163390342</v>
+        <v>0.180373020944776</v>
       </c>
       <c r="I31" s="28" t="n">
         <f aca="false">I30/I7</f>
-        <v>0.181439138444568</v>
+        <v>0.198528912181474</v>
       </c>
       <c r="J31" s="28" t="n">
         <f aca="false">J30/J7</f>
-        <v>0.192884646031465</v>
+        <v>0.219468176206511</v>
       </c>
       <c r="K31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B32" s="28" t="n">
         <f aca="false">-B29/B28</f>
@@ -5520,7 +5640,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B34" s="26" t="n">
         <v>997</v>
@@ -5557,8 +5677,8 @@
       <c r="K34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
-        <v>175</v>
+      <c r="A35" s="18" t="s">
+        <v>183</v>
       </c>
       <c r="B35" s="32" t="n">
         <f aca="false">B30/B34</f>
@@ -5578,23 +5698,23 @@
       </c>
       <c r="F35" s="32" t="n">
         <f aca="false">F30/F34</f>
-        <v>7.94560763742244</v>
+        <v>7.92824223447494</v>
       </c>
       <c r="G35" s="32" t="n">
         <f aca="false">G30/G34</f>
-        <v>9.71439186707335</v>
+        <v>10.0911653596999</v>
       </c>
       <c r="H35" s="32" t="n">
         <f aca="false">H30/H34</f>
-        <v>11.7133215124883</v>
+        <v>12.4924767497909</v>
       </c>
       <c r="I35" s="32" t="n">
         <f aca="false">I30/I34</f>
-        <v>13.9787666143449</v>
+        <v>15.2954282817677</v>
       </c>
       <c r="J35" s="32" t="n">
         <f aca="false">J30/J34</f>
-        <v>16.3916779153732</v>
+        <v>18.6507932646161</v>
       </c>
       <c r="K35" s="2"/>
     </row>
@@ -5612,23 +5732,23 @@
       <c r="K36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
+      <c r="A37" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
       <c r="K37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B38" s="26" t="n">
         <v>3279</v>
@@ -5666,7 +5786,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -5700,7 +5820,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -5736,7 +5856,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B41" s="26" t="n">
         <v>3786</v>
@@ -5773,8 +5893,8 @@
       <c r="K41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
-        <v>181</v>
+      <c r="A42" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="B42" s="27" t="n">
         <f aca="false">B21+B41</f>
@@ -5794,29 +5914,29 @@
       </c>
       <c r="F42" s="27" t="n">
         <f aca="false">F21+F41</f>
-        <v>11943.40658</v>
+        <v>11924.67787</v>
       </c>
       <c r="G42" s="27" t="n">
         <f aca="false">G21+G41</f>
-        <v>13646.5135632</v>
+        <v>14043.2377984</v>
       </c>
       <c r="H42" s="27" t="n">
         <f aca="false">H21+H41</f>
-        <v>15125.82082256</v>
+        <v>15927.530227856</v>
       </c>
       <c r="I42" s="27" t="n">
         <f aca="false">I21+I41</f>
-        <v>16699.5728850563</v>
+        <v>18025.6606082464</v>
       </c>
       <c r="J42" s="27" t="n">
         <f aca="false">J21+J41</f>
-        <v>17946.3596118318</v>
+        <v>20179.5915241081</v>
       </c>
       <c r="K42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -5830,29 +5950,29 @@
       </c>
       <c r="F43" s="27" t="n">
         <f aca="false">F21+F38+F39+F19</f>
-        <v>15617.39786</v>
+        <v>15598.66915</v>
       </c>
       <c r="G43" s="27" t="n">
         <f aca="false">G21+G38+G39+G19</f>
-        <v>17530.8949456</v>
+        <v>17927.6191808</v>
       </c>
       <c r="H43" s="27" t="n">
         <f aca="false">H21+H38+H39+H19</f>
-        <v>19416.748516912</v>
+        <v>20218.457922208</v>
       </c>
       <c r="I43" s="27" t="n">
         <f aca="false">I21+I38+I39+I19</f>
-        <v>21428.7534631213</v>
+        <v>22754.8411863114</v>
       </c>
       <c r="J43" s="27" t="n">
         <f aca="false">J21+J38+J39+J19</f>
-        <v>23100.1251764154</v>
+        <v>25333.3570886917</v>
       </c>
       <c r="K43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -5866,23 +5986,23 @@
       </c>
       <c r="F44" s="28" t="n">
         <f aca="false">F43/F7</f>
-        <v>0.337929489931399</v>
+        <v>0.337524237822558</v>
       </c>
       <c r="G44" s="28" t="n">
         <f aca="false">G43/G7</f>
-        <v>0.341141434704344</v>
+        <v>0.348861466978685</v>
       </c>
       <c r="H44" s="28" t="n">
         <f aca="false">H43/H7</f>
-        <v>0.344812542880615</v>
+        <v>0.359049708204698</v>
       </c>
       <c r="I44" s="28" t="n">
         <f aca="false">I43/I7</f>
-        <v>0.347301228167732</v>
+        <v>0.368793467355357</v>
       </c>
       <c r="J44" s="28" t="n">
         <f aca="false">J43/J7</f>
-        <v>0.344587595126811</v>
+        <v>0.377901008285169</v>
       </c>
       <c r="K44" s="2"/>
     </row>
@@ -5911,7 +6031,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5925,7 +6045,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5951,39 +6071,39 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -5995,28 +6115,28 @@
       </c>
       <c r="F5" s="31" t="n">
         <f aca="false">CF!F30</f>
-        <v>15727.0747355025</v>
+        <v>15712.5225278325</v>
       </c>
       <c r="G5" s="31" t="n">
         <f aca="false">CF!G30</f>
-        <v>22778.3423115682</v>
+        <v>22919.2901759076</v>
       </c>
       <c r="H5" s="31" t="n">
         <f aca="false">CF!H30</f>
-        <v>30551.9375996511</v>
+        <v>31009.6309819474</v>
       </c>
       <c r="I5" s="31" t="n">
         <f aca="false">CF!I30</f>
-        <v>39192.3872970024</v>
+        <v>40177.3067851215</v>
       </c>
       <c r="J5" s="31" t="n">
         <f aca="false">CF!J30</f>
-        <v>48469.3169993497</v>
+        <v>50345.276796753</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -6049,7 +6169,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -6082,7 +6202,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -6115,7 +6235,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6148,7 +6268,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -6181,7 +6301,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -6214,7 +6334,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -6247,7 +6367,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -6280,7 +6400,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -6313,7 +6433,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -6345,8 +6465,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>197</v>
+      <c r="A16" s="18" t="s">
+        <v>205</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -6360,23 +6480,23 @@
       </c>
       <c r="F16" s="30" t="n">
         <f aca="false">SUM(F5:F15)</f>
-        <v>122823.78952016</v>
+        <v>122809.23731249</v>
       </c>
       <c r="G16" s="30" t="n">
         <f aca="false">SUM(G5:G15)</f>
-        <v>131004.750254533</v>
+        <v>131145.698118872</v>
       </c>
       <c r="H16" s="30" t="n">
         <f aca="false">SUM(H5:H15)</f>
-        <v>140023.98982723</v>
+        <v>140481.683209526</v>
       </c>
       <c r="I16" s="30" t="n">
         <f aca="false">SUM(I5:I15)</f>
-        <v>150498.627658342</v>
+        <v>151483.547146461</v>
       </c>
       <c r="J16" s="30" t="n">
         <f aca="false">SUM(J5:J15)</f>
-        <v>162301.902380928</v>
+        <v>164177.862178331</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6393,7 +6513,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -6426,7 +6546,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -6459,7 +6579,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -6492,7 +6612,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -6525,7 +6645,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -6557,8 +6677,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
-        <v>203</v>
+      <c r="A23" s="18" t="s">
+        <v>211</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -6605,7 +6725,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -6638,7 +6758,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -6654,24 +6774,24 @@
       </c>
       <c r="G26" s="27" t="n">
         <f aca="false">F26+CF!G23</f>
-        <v>-67833.2675760658</v>
+        <v>-67988.7676480751</v>
       </c>
       <c r="H26" s="27" t="n">
         <f aca="false">G26+CF!H23</f>
-        <v>-76238.5628641486</v>
+        <v>-76710.8084541149</v>
       </c>
       <c r="I26" s="27" t="n">
         <f aca="false">H26+CF!I23</f>
-        <v>-85592.2975615</v>
+        <v>-86591.769257289</v>
       </c>
       <c r="J26" s="27" t="n">
         <f aca="false">I26+CF!J23</f>
-        <v>-95668.1765138472</v>
+        <v>-97558.6885189205</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -6683,28 +6803,28 @@
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">E27+IS!F30+CF!F24</f>
-        <v>27399.41920016</v>
+        <v>27384.86699249</v>
       </c>
       <c r="G27" s="27" t="n">
         <f aca="false">F27+IS!G30+CF!G24</f>
-        <v>33863.9696789984</v>
+        <v>34160.4176153471</v>
       </c>
       <c r="H27" s="27" t="n">
         <f aca="false">G27+IS!H30+CF!H24</f>
-        <v>41755.7687504108</v>
+        <v>42685.7077226733</v>
       </c>
       <c r="I27" s="27" t="n">
         <f aca="false">H27+IS!I30+CF!I24</f>
-        <v>51237.4184380936</v>
+        <v>53221.8096220017</v>
       </c>
       <c r="J27" s="27" t="n">
         <f aca="false">I27+IS!J30+CF!J24</f>
-        <v>62368.8808771612</v>
+        <v>66135.3526796377</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>207</v>
+      <c r="A28" s="18" t="s">
+        <v>215</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -6718,28 +6838,28 @@
       </c>
       <c r="F28" s="30" t="n">
         <f aca="false">SUM(F25:F27)</f>
-        <v>41156.26088016</v>
+        <v>41141.70867249</v>
       </c>
       <c r="G28" s="30" t="n">
         <f aca="false">SUM(G25:G27)</f>
-        <v>45280.8253713326</v>
+        <v>45421.773235672</v>
       </c>
       <c r="H28" s="30" t="n">
         <f aca="false">SUM(H25:H27)</f>
-        <v>50441.1444208942</v>
+        <v>50898.8378031904</v>
       </c>
       <c r="I28" s="30" t="n">
         <f aca="false">SUM(I25:I27)</f>
-        <v>56690.223384133</v>
+        <v>57675.142872252</v>
       </c>
       <c r="J28" s="30" t="n">
         <f aca="false">SUM(J25:J27)</f>
-        <v>64309.8794514026</v>
+        <v>66185.8392488058</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>208</v>
+      <c r="A29" s="18" t="s">
+        <v>216</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -6753,23 +6873,23 @@
       </c>
       <c r="F29" s="27" t="n">
         <f aca="false">F23+F28</f>
-        <v>122823.78952016</v>
+        <v>122809.23731249</v>
       </c>
       <c r="G29" s="27" t="n">
         <f aca="false">G23+G28</f>
-        <v>131004.750254533</v>
+        <v>131145.698118872</v>
       </c>
       <c r="H29" s="27" t="n">
         <f aca="false">H23+H28</f>
-        <v>140023.98982723</v>
+        <v>140481.683209526</v>
       </c>
       <c r="I29" s="27" t="n">
         <f aca="false">I23+I28</f>
-        <v>150498.627658342</v>
+        <v>151483.547146461</v>
       </c>
       <c r="J29" s="27" t="n">
         <f aca="false">J23+J28</f>
-        <v>162301.902380928</v>
+        <v>164177.862178331</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6785,8 +6905,8 @@
       <c r="J30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
-        <v>209</v>
+      <c r="A31" s="18" t="s">
+        <v>217</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -6833,7 +6953,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -6847,28 +6967,28 @@
       </c>
       <c r="F33" s="27" t="n">
         <f aca="false">F5+F6-F21</f>
-        <v>-21315.9252644975</v>
+        <v>-21330.4774721675</v>
       </c>
       <c r="G33" s="27" t="n">
         <f aca="false">G5+G6-G21</f>
-        <v>-14264.6576884318</v>
+        <v>-14123.7098240924</v>
       </c>
       <c r="H33" s="27" t="n">
         <f aca="false">H5+H6-H21</f>
-        <v>-6491.06240034892</v>
+        <v>-6033.36901805264</v>
       </c>
       <c r="I33" s="27" t="n">
         <f aca="false">I5+I6-I21</f>
-        <v>2149.38729700244</v>
+        <v>3134.3067851215</v>
       </c>
       <c r="J33" s="27" t="n">
         <f aca="false">J5+J6-J21</f>
-        <v>11426.3169993497</v>
+        <v>13302.276796753</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -6882,23 +7002,23 @@
       </c>
       <c r="F34" s="34" t="n">
         <f aca="false">F21/IS!F42</f>
-        <v>3.28892763860007</v>
+        <v>3.29409317620418</v>
       </c>
       <c r="G34" s="34" t="n">
         <f aca="false">G21/IS!G42</f>
-        <v>2.87846414529844</v>
+        <v>2.79714696595649</v>
       </c>
       <c r="H34" s="34" t="n">
         <f aca="false">H21/IS!H42</f>
-        <v>2.5969499745371</v>
+        <v>2.46623295878608</v>
       </c>
       <c r="I34" s="34" t="n">
         <f aca="false">I21/IS!I42</f>
-        <v>2.35221584829578</v>
+        <v>2.17917117456598</v>
       </c>
       <c r="J34" s="34" t="n">
         <f aca="false">J21/IS!J42</f>
-        <v>2.188800450321</v>
+        <v>1.94657062077158</v>
       </c>
     </row>
   </sheetData>
@@ -6926,7 +7046,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6940,7 +7060,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6966,39 +7086,39 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B5" s="31" t="n">
         <f aca="false">IS!B30</f>
@@ -7018,28 +7138,28 @@
       </c>
       <c r="F5" s="31" t="n">
         <f aca="false">IS!F30</f>
-        <v>6658.41920016</v>
+        <v>6643.86699249</v>
       </c>
       <c r="G5" s="31" t="n">
         <f aca="false">IS!G30</f>
-        <v>8018.55047883836</v>
+        <v>8329.55062285707</v>
       </c>
       <c r="H5" s="31" t="n">
         <f aca="false">IS!H30</f>
-        <v>9523.49907141239</v>
+        <v>10156.9901073262</v>
       </c>
       <c r="I5" s="31" t="n">
         <f aca="false">IS!I30</f>
-        <v>11194.9346876828</v>
+        <v>12249.3868993284</v>
       </c>
       <c r="J5" s="31" t="n">
         <f aca="false">IS!J30</f>
-        <v>12930.4116890676</v>
+        <v>14712.492307636</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B6" s="31" t="n">
         <f aca="false">IS!B41</f>
@@ -7080,7 +7200,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B7" s="31" t="n">
         <f aca="false">IS!B38</f>
@@ -7121,7 +7241,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -7150,7 +7270,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -7179,7 +7299,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -7208,7 +7328,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7237,7 +7357,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B12" s="26" t="n">
         <v>1744</v>
@@ -7274,7 +7394,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B13" s="27" t="n">
         <f aca="false">B15-SUM(B5:B12)</f>
@@ -7314,8 +7434,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>223</v>
+      <c r="A14" s="18" t="s">
+        <v>231</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">SUM(B5:B13)</f>
@@ -7335,28 +7455,28 @@
       </c>
       <c r="F14" s="30" t="n">
         <f aca="false">SUM(F5:F13)</f>
-        <v>14235.2991355025</v>
+        <v>14220.7469278325</v>
       </c>
       <c r="G14" s="30" t="n">
         <f aca="false">SUM(G5:G13)</f>
-        <v>15981.3691741315</v>
+        <v>16292.3693181502</v>
       </c>
       <c r="H14" s="30" t="n">
         <f aca="false">SUM(H5:H13)</f>
-        <v>17655.2559857257</v>
+        <v>18288.7470216396</v>
       </c>
       <c r="I14" s="30" t="n">
         <f aca="false">SUM(I5:I13)</f>
-        <v>19632.9809560715</v>
+        <v>20687.4331677171</v>
       </c>
       <c r="J14" s="30" t="n">
         <f aca="false">SUM(J5:J13)</f>
-        <v>21157.313190336</v>
+        <v>22939.3938089044</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B15" s="26" t="n">
         <v>7111</v>
@@ -7378,7 +7498,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B16" s="26" t="n">
         <v>-798</v>
@@ -7415,7 +7535,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -7448,7 +7568,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -7476,8 +7596,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>228</v>
+      <c r="A19" s="18" t="s">
+        <v>236</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -7518,7 +7638,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -7551,7 +7671,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -7584,7 +7704,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B23" s="26" t="n">
         <v>-4000</v>
@@ -7604,24 +7724,24 @@
       </c>
       <c r="G23" s="27" t="n">
         <f aca="false">-Assumptions!G54*MAX(G32,0)</f>
-        <v>-7605.26757606575</v>
+        <v>-7760.76764807511</v>
       </c>
       <c r="H23" s="27" t="n">
         <f aca="false">-Assumptions!H54*MAX(H32,0)</f>
-        <v>-8405.29528808286</v>
+        <v>-8722.04080603978</v>
       </c>
       <c r="I23" s="27" t="n">
         <f aca="false">-Assumptions!I54*MAX(I32,0)</f>
-        <v>-9353.73469735136</v>
+        <v>-9880.96080317414</v>
       </c>
       <c r="J23" s="27" t="n">
         <f aca="false">-Assumptions!J54*MAX(J32,0)</f>
-        <v>-10075.8789523473</v>
+        <v>-10966.9192616315</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B24" s="26" t="n">
         <v>0</v>
@@ -7658,7 +7778,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -7690,8 +7810,8 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
-        <v>234</v>
+      <c r="A26" s="18" t="s">
+        <v>242</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -7703,19 +7823,19 @@
       </c>
       <c r="G26" s="30" t="n">
         <f aca="false">SUM(G21:G25)</f>
-        <v>-8159.26757606575</v>
+        <v>-8314.76764807511</v>
       </c>
       <c r="H26" s="30" t="n">
         <f aca="false">SUM(H21:H25)</f>
-        <v>-9036.99528808286</v>
+        <v>-9353.74080603978</v>
       </c>
       <c r="I26" s="30" t="n">
         <f aca="false">SUM(I21:I25)</f>
-        <v>-10067.0196973514</v>
+        <v>-10594.2458031741</v>
       </c>
       <c r="J26" s="30" t="n">
         <f aca="false">SUM(J21:J25)</f>
-        <v>-10874.8282023473</v>
+        <v>-11765.8685116315</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7731,8 +7851,8 @@
       <c r="J27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>235</v>
+      <c r="A28" s="18" t="s">
+        <v>243</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -7740,28 +7860,28 @@
       <c r="E28" s="2"/>
       <c r="F28" s="27" t="n">
         <f aca="false">F14+F19+F26</f>
-        <v>8400.07473550247</v>
+        <v>8385.52252783247</v>
       </c>
       <c r="G28" s="27" t="n">
         <f aca="false">G14+G19+G26</f>
-        <v>7051.26757606575</v>
+        <v>7206.76764807511</v>
       </c>
       <c r="H28" s="27" t="n">
         <f aca="false">H14+H19+H26</f>
-        <v>7773.59528808286</v>
+        <v>8090.34080603978</v>
       </c>
       <c r="I28" s="27" t="n">
         <f aca="false">I14+I19+I26</f>
-        <v>8640.44969735136</v>
+        <v>9167.67580317414</v>
       </c>
       <c r="J28" s="27" t="n">
         <f aca="false">J14+J19+J26</f>
-        <v>9276.92970234727</v>
+        <v>10167.9700116315</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -7773,24 +7893,24 @@
       </c>
       <c r="G29" s="31" t="n">
         <f aca="false">BS!F5</f>
-        <v>15727.0747355025</v>
+        <v>15712.5225278325</v>
       </c>
       <c r="H29" s="31" t="n">
         <f aca="false">BS!G5</f>
-        <v>22778.3423115682</v>
+        <v>22919.2901759076</v>
       </c>
       <c r="I29" s="31" t="n">
         <f aca="false">BS!H5</f>
-        <v>30551.9375996511</v>
+        <v>31009.6309819474</v>
       </c>
       <c r="J29" s="31" t="n">
         <f aca="false">BS!I5</f>
-        <v>39192.3872970024</v>
+        <v>40177.3067851215</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
-        <v>237</v>
+      <c r="A30" s="18" t="s">
+        <v>245</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -7798,23 +7918,23 @@
       <c r="E30" s="2"/>
       <c r="F30" s="30" t="n">
         <f aca="false">F29+F28</f>
-        <v>15727.0747355025</v>
+        <v>15712.5225278325</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">G29+G28</f>
-        <v>22778.3423115682</v>
+        <v>22919.2901759076</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">H29+H28</f>
-        <v>30551.9375996511</v>
+        <v>31009.6309819474</v>
       </c>
       <c r="I30" s="30" t="n">
         <f aca="false">I29+I28</f>
-        <v>39192.3872970024</v>
+        <v>40177.3067851215</v>
       </c>
       <c r="J30" s="30" t="n">
         <f aca="false">J29+J28</f>
-        <v>48469.3169993497</v>
+        <v>50345.276796753</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7830,8 +7950,8 @@
       <c r="J31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
-        <v>238</v>
+      <c r="A32" s="18" t="s">
+        <v>246</v>
       </c>
       <c r="B32" s="27" t="n">
         <f aca="false">B14+B16</f>
@@ -7851,28 +7971,28 @@
       </c>
       <c r="F32" s="27" t="n">
         <f aca="false">F14+F16</f>
-        <v>13542.0747355025</v>
+        <v>13527.5225278325</v>
       </c>
       <c r="G32" s="27" t="n">
         <f aca="false">G14+G16</f>
-        <v>15210.5351521315</v>
+        <v>15521.5352961502</v>
       </c>
       <c r="H32" s="27" t="n">
         <f aca="false">H14+H16</f>
-        <v>16810.5905761657</v>
+        <v>17444.0816120796</v>
       </c>
       <c r="I32" s="27" t="n">
         <f aca="false">I14+I16</f>
-        <v>18707.4693947027</v>
+        <v>19761.9216063483</v>
       </c>
       <c r="J32" s="27" t="n">
         <f aca="false">J14+J16</f>
-        <v>20151.7579046945</v>
+        <v>21933.8385232629</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B33" s="28" t="n">
         <f aca="false">B32/IS!B7</f>
@@ -7892,28 +8012,28 @@
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">F32/IS!F7</f>
-        <v>0.293023616930589</v>
+        <v>0.292708736042019</v>
       </c>
       <c r="G33" s="28" t="n">
         <f aca="false">G32/IS!G7</f>
-        <v>0.295988527711835</v>
+        <v>0.302040416999463</v>
       </c>
       <c r="H33" s="28" t="n">
         <f aca="false">H32/IS!H7</f>
-        <v>0.298531058320287</v>
+        <v>0.309780915874721</v>
       </c>
       <c r="I33" s="28" t="n">
         <f aca="false">I32/IS!I7</f>
-        <v>0.303196688872827</v>
+        <v>0.320286462609733</v>
       </c>
       <c r="J33" s="28" t="n">
         <f aca="false">J32/IS!J7</f>
-        <v>0.30060641407459</v>
+        <v>0.327189944249636</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="28" t="n">
@@ -7930,28 +8050,28 @@
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">F32/E32-1</f>
-        <v>-0.0597087393763039</v>
+        <v>-0.0607191690159374</v>
       </c>
       <c r="G34" s="28" t="n">
         <f aca="false">G32/F32-1</f>
-        <v>0.123205671894199</v>
+        <v>0.147404135843436</v>
       </c>
       <c r="H34" s="28" t="n">
         <f aca="false">H32/G32-1</f>
-        <v>0.105193894102403</v>
+        <v>0.123863153950124</v>
       </c>
       <c r="I34" s="28" t="n">
         <f aca="false">I32/H32-1</f>
-        <v>0.112838321172751</v>
+        <v>0.132872572246147</v>
       </c>
       <c r="J34" s="28" t="n">
         <f aca="false">J32/I32-1</f>
-        <v>0.0772038419264123</v>
+        <v>0.109904135851695</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">B32-B7</f>
@@ -7971,23 +8091,23 @@
       </c>
       <c r="F35" s="27" t="n">
         <f aca="false">F32-F7</f>
-        <v>9706.23305550247</v>
+        <v>9691.68084783247</v>
       </c>
       <c r="G35" s="27" t="n">
         <f aca="false">G32-G7</f>
-        <v>10945.2535637315</v>
+        <v>11256.2537077502</v>
       </c>
       <c r="H35" s="27" t="n">
         <f aca="false">H32-H7</f>
-        <v>12136.7753099337</v>
+        <v>12770.2663458476</v>
       </c>
       <c r="I35" s="27" t="n">
         <f aca="false">I32-I7</f>
-        <v>13586.3054217954</v>
+        <v>14640.7576334409</v>
       </c>
       <c r="J35" s="27" t="n">
         <f aca="false">J32-J7</f>
-        <v>14587.6853241453</v>
+        <v>16369.7659427137</v>
       </c>
     </row>
   </sheetData>
@@ -8016,7 +8136,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8031,7 +8151,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8058,23 +8178,23 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
+      <c r="A4" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B5" s="35" t="n">
         <v>46309</v>
@@ -8091,7 +8211,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B6" s="36" t="n">
         <v>235.95</v>
@@ -8105,12 +8225,12 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B7" s="26" t="n">
         <v>823</v>
@@ -8124,12 +8244,12 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B8" s="26" t="n">
         <v>7</v>
@@ -8143,12 +8263,12 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>252</v>
+      <c r="A9" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">B7+B8</f>
@@ -8166,7 +8286,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B10" s="35" t="n">
         <v>46234</v>
@@ -8180,12 +8300,12 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B11" s="26" t="n">
         <v>8310</v>
@@ -8199,12 +8319,12 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B12" s="26" t="n">
         <v>3093</v>
@@ -8218,12 +8338,12 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="3" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B13" s="26" t="n">
         <v>11324</v>
@@ -8237,14 +8357,14 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B14" s="22" t="n">
+        <v>266</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <v>0.2</v>
       </c>
       <c r="C14" s="2"/>
@@ -8256,12 +8376,12 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="3" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B15" s="26" t="n">
         <v>39288</v>
@@ -8275,14 +8395,14 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B16" s="18" t="n">
+        <v>270</v>
+      </c>
+      <c r="B16" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="2"/>
@@ -8294,7 +8414,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8311,26 +8431,26 @@
       <c r="K17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
+      <c r="A18" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
       <c r="K18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B19" s="25" t="n">
-        <v>0.052</v>
+        <v>0.0521</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -8341,12 +8461,12 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="3" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B20" s="25" t="n">
         <v>0.05</v>
@@ -8360,12 +8480,12 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B21" s="38" t="n">
         <v>1.26</v>
@@ -8379,16 +8499,16 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="3" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="B22" s="23" t="n">
+      <c r="A22" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B22" s="12" t="n">
         <f aca="false">B19+B21*B20</f>
-        <v>0.115</v>
+        <v>0.1151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -8402,7 +8522,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B23" s="25" t="n">
         <v>0.055</v>
@@ -8416,12 +8536,12 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B24" s="25" t="n">
         <v>0.21</v>
@@ -8435,12 +8555,12 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="3" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B25" s="28" t="n">
         <f aca="false">B23*(1-B24)</f>
@@ -8458,7 +8578,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B26" s="27" t="n">
         <f aca="false">B6*B9</f>
@@ -8476,7 +8596,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B27" s="27" t="n">
         <f aca="false">B15</f>
@@ -8494,7 +8614,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B28" s="28" t="n">
         <f aca="false">B26/(B26+B27)</f>
@@ -8512,7 +8632,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B29" s="28" t="n">
         <f aca="false">B27/(B26+B27)</f>
@@ -8529,12 +8649,12 @@
       <c r="K29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="39" t="n">
         <f aca="false">B28*B22+B29*B25</f>
-        <v>0.103044493496054</v>
+        <v>0.103127784192764</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -8560,25 +8680,25 @@
       <c r="K31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
+      <c r="A32" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
       <c r="K32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="B33" s="22" t="n">
+        <v>290</v>
+      </c>
+      <c r="B33" s="23" t="n">
         <v>0.03</v>
       </c>
       <c r="C33" s="2"/>
@@ -8590,15 +8710,15 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B34" s="40" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -8609,15 +8729,15 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B35" s="25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -8627,7 +8747,9 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
+      <c r="K35" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
@@ -8644,32 +8766,32 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
-      <c r="F37" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I37" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J37" s="19" t="s">
-        <v>45</v>
+      <c r="F37" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="K37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -8699,7 +8821,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -8729,7 +8851,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -8737,29 +8859,29 @@
       <c r="E40" s="2"/>
       <c r="F40" s="31" t="n">
         <f aca="false">IS!F21</f>
-        <v>9419.40658000001</v>
+        <v>9400.67787</v>
       </c>
       <c r="G40" s="31" t="n">
         <f aca="false">IS!G21</f>
-        <v>11308.6686832</v>
+        <v>11705.3929184</v>
       </c>
       <c r="H40" s="31" t="n">
         <f aca="false">IS!H21</f>
-        <v>12961.37811416</v>
+        <v>13763.087519456</v>
       </c>
       <c r="I40" s="31" t="n">
         <f aca="false">IS!I21</f>
-        <v>14799.0856364243</v>
+        <v>16125.1733596144</v>
       </c>
       <c r="J40" s="31" t="n">
         <f aca="false">IS!J21</f>
-        <v>16685.8675006524</v>
+        <v>18919.0994129287</v>
       </c>
       <c r="K40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -8767,29 +8889,29 @@
       <c r="E41" s="2"/>
       <c r="F41" s="27" t="n">
         <f aca="false">-F40*Assumptions!F38</f>
-        <v>-2100.52766734</v>
+        <v>-2096.35116501</v>
       </c>
       <c r="G41" s="27" t="n">
         <f aca="false">-G40*Assumptions!G38</f>
-        <v>-2431.363766888</v>
+        <v>-2516.659477456</v>
       </c>
       <c r="H41" s="27" t="n">
         <f aca="false">-H40*Assumptions!H38</f>
-        <v>-2786.6962945444</v>
+        <v>-2959.06381668304</v>
       </c>
       <c r="I41" s="27" t="n">
         <f aca="false">-I40*Assumptions!I38</f>
-        <v>-3181.80341183123</v>
+        <v>-3466.9122723171</v>
       </c>
       <c r="J41" s="27" t="n">
         <f aca="false">-J40*Assumptions!J38</f>
-        <v>-3587.46151264027</v>
+        <v>-4067.60637377967</v>
       </c>
       <c r="K41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
-        <v>292</v>
+      <c r="A42" s="18" t="s">
+        <v>301</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -8797,29 +8919,29 @@
       <c r="E42" s="2"/>
       <c r="F42" s="27" t="n">
         <f aca="false">F40+F41</f>
-        <v>7318.87891266001</v>
+        <v>7304.32670499</v>
       </c>
       <c r="G42" s="27" t="n">
         <f aca="false">G40+G41</f>
-        <v>8877.304916312</v>
+        <v>9188.733440944</v>
       </c>
       <c r="H42" s="27" t="n">
         <f aca="false">H40+H41</f>
-        <v>10174.6818196156</v>
+        <v>10804.023702773</v>
       </c>
       <c r="I42" s="27" t="n">
         <f aca="false">I40+I41</f>
-        <v>11617.2822245931</v>
+        <v>12658.2610872973</v>
       </c>
       <c r="J42" s="27" t="n">
         <f aca="false">J40+J41</f>
-        <v>13098.4059880121</v>
+        <v>14851.493039149</v>
       </c>
       <c r="K42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -8849,7 +8971,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -8879,7 +9001,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -8909,7 +9031,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -8938,8 +9060,8 @@
       <c r="K46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="s">
-        <v>297</v>
+      <c r="A47" s="18" t="s">
+        <v>306</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -8947,29 +9069,29 @@
       <c r="E47" s="2"/>
       <c r="F47" s="30" t="n">
         <f aca="false">SUM(F42:F46)</f>
-        <v>10366.6927680025</v>
+        <v>10352.1405603325</v>
       </c>
       <c r="G47" s="30" t="n">
         <f aca="false">SUM(G42:G46)</f>
-        <v>11804.0080012052</v>
+        <v>12115.4365258372</v>
       </c>
       <c r="H47" s="30" t="n">
         <f aca="false">SUM(H42:H46)</f>
-        <v>12787.9580581369</v>
+        <v>13417.2999412943</v>
       </c>
       <c r="I47" s="30" t="n">
         <f aca="false">SUM(I42:I46)</f>
-        <v>14008.6529587056</v>
+        <v>15049.6318214098</v>
       </c>
       <c r="J47" s="30" t="n">
         <f aca="false">SUM(J42:J46)</f>
-        <v>14755.6796230898</v>
+        <v>16508.7666742267</v>
       </c>
       <c r="K47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -8977,29 +9099,29 @@
       <c r="E48" s="2"/>
       <c r="F48" s="28" t="n">
         <f aca="false">F47/F39</f>
-        <v>0.224314654129366</v>
+        <v>0.223999773240796</v>
       </c>
       <c r="G48" s="28" t="n">
         <f aca="false">G47/G39</f>
-        <v>0.229699409943892</v>
+        <v>0.23575963527925</v>
       </c>
       <c r="H48" s="28" t="n">
         <f aca="false">H47/H39</f>
-        <v>0.227095094342712</v>
+        <v>0.238271269122117</v>
       </c>
       <c r="I48" s="28" t="n">
         <f aca="false">I47/I39</f>
-        <v>0.227041782243984</v>
+        <v>0.24391319000627</v>
       </c>
       <c r="J48" s="28" t="n">
         <f aca="false">J47/J39</f>
-        <v>0.220112407051952</v>
+        <v>0.246263436381264</v>
       </c>
       <c r="K48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -9029,7 +9151,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -9037,29 +9159,29 @@
       <c r="E50" s="2"/>
       <c r="F50" s="27" t="n">
         <f aca="false">F47*F49</f>
-        <v>5225.94923099303</v>
+        <v>5218.61332356486</v>
       </c>
       <c r="G50" s="27" t="n">
         <f aca="false">G47*G49</f>
-        <v>11804.0080012052</v>
+        <v>12115.4365258372</v>
       </c>
       <c r="H50" s="27" t="n">
         <f aca="false">H47*H49</f>
-        <v>12787.9580581369</v>
+        <v>13417.2999412943</v>
       </c>
       <c r="I50" s="27" t="n">
         <f aca="false">I47*I49</f>
-        <v>14008.6529587056</v>
+        <v>15049.6318214098</v>
       </c>
       <c r="J50" s="27" t="n">
         <f aca="false">J47*J49</f>
-        <v>14755.6796230898</v>
+        <v>16508.7666742267</v>
       </c>
       <c r="K50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -9089,7 +9211,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -9097,29 +9219,29 @@
       <c r="E52" s="2"/>
       <c r="F52" s="43" t="n">
         <f aca="false">1/(1+$B$30)^F51</f>
-        <v>0.995442582912682</v>
+        <v>0.995439082183007</v>
       </c>
       <c r="G52" s="43" t="n">
         <f aca="false">1/(1+$B$30)^G51</f>
-        <v>0.924663941092435</v>
+        <v>0.92460818355433</v>
       </c>
       <c r="H52" s="43" t="n">
         <f aca="false">1/(1+$B$30)^H51</f>
-        <v>0.838058234568608</v>
+        <v>0.837944253001688</v>
       </c>
       <c r="I52" s="43" t="n">
         <f aca="false">1/(1+$B$30)^I51</f>
-        <v>0.759768295395245</v>
+        <v>0.759607603950317</v>
       </c>
       <c r="J52" s="43" t="n">
         <f aca="false">1/(1+$B$30)^J51</f>
-        <v>0.688792065846039</v>
+        <v>0.688594390273811</v>
       </c>
       <c r="K52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="17" t="s">
-        <v>303</v>
+      <c r="A53" s="18" t="s">
+        <v>312</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -9127,23 +9249,23 @@
       <c r="E53" s="2"/>
       <c r="F53" s="27" t="n">
         <f aca="false">F50*F52</f>
-        <v>5202.13240067024</v>
+        <v>5194.81165707742</v>
       </c>
       <c r="G53" s="27" t="n">
         <f aca="false">G50*G52</f>
-        <v>10914.740559081</v>
+        <v>11202.0317591221</v>
       </c>
       <c r="H53" s="27" t="n">
         <f aca="false">H50*H52</f>
-        <v>10717.0535539396</v>
+        <v>11242.9493766074</v>
       </c>
       <c r="I53" s="27" t="n">
         <f aca="false">I50*I52</f>
-        <v>10643.3303792193</v>
+        <v>11431.8147681956</v>
       </c>
       <c r="J53" s="27" t="n">
         <f aca="false">J50*J52</f>
-        <v>10163.5950505503</v>
+        <v>11367.8441222118</v>
       </c>
       <c r="K53" s="2"/>
     </row>
@@ -9161,27 +9283,27 @@
       <c r="K54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
+      <c r="A55" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
       <c r="K55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B56" s="27" t="n">
         <f aca="false">SUM(F53:J53)</f>
-        <v>47640.8519434605</v>
+        <v>50439.4516832142</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -9195,7 +9317,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B57" s="42" t="n">
         <f aca="false">(J38-B5)/365</f>
@@ -9213,11 +9335,11 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B58" s="27" t="n">
         <f aca="false">J47*(1+B33)</f>
-        <v>15198.3500117825</v>
+        <v>17004.0296744535</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -9231,11 +9353,11 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B59" s="27" t="n">
         <f aca="false">B58/(B30-B33)</f>
-        <v>208069.756998226</v>
+        <v>232524.88588511</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -9249,11 +9371,11 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B60" s="27" t="n">
         <f aca="false">IS!J42*B34</f>
-        <v>287141.753789308</v>
+        <v>262334.689813405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -9267,11 +9389,11 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B61" s="27" t="n">
         <f aca="false">B59/(1+B30)^B57</f>
-        <v>136458.496013609</v>
+        <v>152447.395372357</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -9285,11 +9407,11 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B62" s="27" t="n">
         <f aca="false">B60/(1+B30)^B57</f>
-        <v>188316.32443889</v>
+        <v>171991.225909595</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -9303,11 +9425,11 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B63" s="34" t="n">
         <f aca="false">B59/IS!J42</f>
-        <v>11.5939812585194</v>
+        <v>11.5227746610886</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -9321,11 +9443,11 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B64" s="28" t="n">
         <f aca="false">(B60*B30-J47)/(B60+J47)</f>
-        <v>0.0491315768737802</v>
+        <v>0.0378177373640239</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -9352,16 +9474,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>317</v>
+        <v>323</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>326</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
@@ -9372,20 +9494,20 @@
       <c r="K66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="17" t="s">
-        <v>318</v>
+      <c r="A67" s="18" t="s">
+        <v>327</v>
       </c>
       <c r="B67" s="27" t="n">
         <f aca="false">$B$56+$B$61</f>
-        <v>184099.347957069</v>
+        <v>202886.847055571</v>
       </c>
       <c r="C67" s="27" t="n">
         <f aca="false">$B$56+$B$62</f>
-        <v>235957.17638235</v>
+        <v>222430.677592809</v>
       </c>
       <c r="D67" s="27" t="n">
         <f aca="false">$B$35*B67+(1-$B$35)*C67</f>
-        <v>210028.26216971</v>
+        <v>202886.847055571</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
@@ -9397,7 +9519,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B68" s="27" t="n">
         <f aca="false">$B$11</f>
@@ -9421,7 +9543,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B69" s="27" t="n">
         <f aca="false">$B$12</f>
@@ -9445,7 +9567,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B70" s="27" t="n">
         <f aca="false">$B$13*(1-$B$14)</f>
@@ -9469,7 +9591,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B71" s="27" t="n">
         <f aca="false">-$B$15</f>
@@ -9492,20 +9614,20 @@
       <c r="K71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="17" t="s">
-        <v>323</v>
+      <c r="A72" s="18" t="s">
+        <v>332</v>
       </c>
       <c r="B72" s="30" t="n">
         <f aca="false">SUM(B67:B71)</f>
-        <v>165273.547957069</v>
+        <v>184061.047055571</v>
       </c>
       <c r="C72" s="30" t="n">
         <f aca="false">SUM(C67:C71)</f>
-        <v>217131.37638235</v>
+        <v>203604.877592809</v>
       </c>
       <c r="D72" s="30" t="n">
         <f aca="false">SUM(D67:D71)</f>
-        <v>191202.46216971</v>
+        <v>184061.047055571</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
@@ -9517,7 +9639,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B73" s="27" t="n">
         <f aca="false">$B$9</f>
@@ -9540,20 +9662,20 @@
       <c r="K73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="17" t="s">
-        <v>324</v>
+      <c r="A74" s="18" t="s">
+        <v>333</v>
       </c>
       <c r="B74" s="44" t="n">
         <f aca="false">B72/B73</f>
-        <v>199.124756574782</v>
+        <v>221.760297657315</v>
       </c>
       <c r="C74" s="44" t="n">
         <f aca="false">C72/C73</f>
-        <v>261.604067930543</v>
+        <v>245.307081437119</v>
       </c>
       <c r="D74" s="44" t="n">
         <f aca="false">D72/D73</f>
-        <v>230.364412252662</v>
+        <v>221.760297657315</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
@@ -9565,7 +9687,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B75" s="32" t="n">
         <f aca="false">$B$6</f>
@@ -9589,19 +9711,19 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B76" s="28" t="n">
         <f aca="false">B74/B75-1</f>
-        <v>-0.156072233207111</v>
+        <v>-0.0601385986127792</v>
       </c>
       <c r="C76" s="28" t="n">
         <f aca="false">C74/C75-1</f>
-        <v>0.10872671299234</v>
+        <v>0.0396570520750972</v>
       </c>
       <c r="D76" s="28" t="n">
         <f aca="false">D74/D75-1</f>
-        <v>-0.0236727601073857</v>
+        <v>-0.0601385986127792</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
@@ -9613,19 +9735,19 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B77" s="28" t="n">
         <f aca="false">$B$61/B67</f>
-        <v>0.741222049550278</v>
+        <v>0.751391219217879</v>
       </c>
       <c r="C77" s="28" t="n">
         <f aca="false">$B$62/C67</f>
-        <v>0.798095346478201</v>
+        <v>0.773235183972461</v>
       </c>
       <c r="D77" s="28" t="n">
         <f aca="false">($B$35*$B$61+(1-$B$35)*$B$62)/D67</f>
-        <v>0.773169327540476</v>
+        <v>0.751391219217879</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
@@ -9663,7 +9785,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -9678,7 +9800,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B81" s="45" t="n">
         <f aca="false">$B$33-0.01</f>
@@ -9709,27 +9831,27 @@
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="46" t="n">
         <f aca="false">$B$30+(-0.01)</f>
-        <v>0.0930444934960543</v>
+        <v>0.0931277841927643</v>
       </c>
       <c r="B82" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A82)^$F$51:$J$51)+$J$47*(1+B$81)/($A82-B$81)/(1+$A82)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>205.107940406231</v>
+        <v>228.406591526049</v>
       </c>
       <c r="C82" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A82)^$F$51:$J$51)+$J$47*(1+C$81)/($A82-C$81)/(1+$A82)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>218.440479280989</v>
+        <v>243.284189209082</v>
       </c>
       <c r="D82" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A82)^$F$51:$J$51)+$J$47*(1+D$81)/($A82-D$81)/(1+$A82)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>233.887800611029</v>
+        <v>260.518530103252</v>
       </c>
       <c r="E82" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A82)^$F$51:$J$51)+$J$47*(1+E$81)/($A82-E$81)/(1+$A82)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>251.996411651709</v>
+        <v>280.717776873932</v>
       </c>
       <c r="F82" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A82)^$F$51:$J$51)+$J$47*(1+F$81)/($A82-F$81)/(1+$A82)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>273.518875827217</v>
+        <v>304.719035544335</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -9740,27 +9862,27 @@
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="46" t="n">
         <f aca="false">$B$30+(-0.005)</f>
-        <v>0.0980444934960542</v>
+        <v>0.0981277841927643</v>
       </c>
       <c r="B83" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A83)^$F$51:$J$51)+$J$47*(1+B$81)/($A83-B$81)/(1+$A83)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>190.637791942475</v>
+        <v>212.272757167092</v>
       </c>
       <c r="C83" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A83)^$F$51:$J$51)+$J$47*(1+C$81)/($A83-C$81)/(1+$A83)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>202.088173016023</v>
+        <v>225.052097233087</v>
       </c>
       <c r="D83" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A83)^$F$51:$J$51)+$J$47*(1+D$81)/($A83-D$81)/(1+$A83)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>215.221332590114</v>
+        <v>239.707227069353</v>
       </c>
       <c r="E83" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A83)^$F$51:$J$51)+$J$47*(1+E$81)/($A83-E$81)/(1+$A83)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>230.437649446596</v>
+        <v>256.683859239917</v>
       </c>
       <c r="F83" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A83)^$F$51:$J$51)+$J$47*(1+F$81)/($A83-F$81)/(1+$A83)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>248.275458186285</v>
+        <v>276.581062425931</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -9771,27 +9893,27 @@
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="46" t="n">
         <f aca="false">$B$30+(0)</f>
-        <v>0.103044493496054</v>
+        <v>0.103127784192764</v>
       </c>
       <c r="B84" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A84)^$F$51:$J$51)+$J$47*(1+B$81)/($A84-B$81)/(1+$A84)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>177.923214328043</v>
+        <v>198.096507231309</v>
       </c>
       <c r="C84" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A84)^$F$51:$J$51)+$J$47*(1+C$81)/($A84-C$81)/(1+$A84)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>187.844836247638</v>
+        <v>209.171188136031</v>
       </c>
       <c r="D84" s="47" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A84)^$F$51:$J$51)+$J$47*(1+D$81)/($A84-D$81)/(1+$A84)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>199.124756574782</v>
+        <v>221.760297657315</v>
       </c>
       <c r="E84" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A84)^$F$51:$J$51)+$J$47*(1+E$81)/($A84-E$81)/(1+$A84)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>212.062404037157</v>
+        <v>236.197274340352</v>
       </c>
       <c r="F84" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A84)^$F$51:$J$51)+$J$47*(1+F$81)/($A84-F$81)/(1+$A84)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>227.052197015331</v>
+        <v>252.921195966514</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -9802,27 +9924,27 @@
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="46" t="n">
         <f aca="false">$B$30+(0.005)</f>
-        <v>0.108044493496054</v>
+        <v>0.108127784192764</v>
       </c>
       <c r="B85" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A85)^$F$51:$J$51)+$J$47*(1+B$81)/($A85-B$81)/(1+$A85)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>166.664654708407</v>
+        <v>185.544094307702</v>
       </c>
       <c r="C85" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A85)^$F$51:$J$51)+$J$47*(1+C$81)/($A85-C$81)/(1+$A85)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>175.329050694751</v>
+        <v>195.216620597304</v>
       </c>
       <c r="D85" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A85)^$F$51:$J$51)+$J$47*(1+D$81)/($A85-D$81)/(1+$A85)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>185.103633396161</v>
+        <v>206.127186131144</v>
       </c>
       <c r="E85" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A85)^$F$51:$J$51)+$J$47*(1+E$81)/($A85-E$81)/(1+$A85)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>196.216384415754</v>
+        <v>218.529738008379</v>
       </c>
       <c r="F85" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A85)^$F$51:$J$51)+$J$47*(1+F$81)/($A85-F$81)/(1+$A85)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>208.962294923885</v>
+        <v>232.7527735582</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -9833,27 +9955,27 @@
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="46" t="n">
         <f aca="false">$B$30+(0.01)</f>
-        <v>0.113044493496054</v>
+        <v>0.113127784192764</v>
       </c>
       <c r="B86" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A86)^$F$51:$J$51)+$J$47*(1+B$81)/($A86-B$81)/(1+$A86)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>156.626966178411</v>
+        <v>174.353465814256</v>
       </c>
       <c r="C86" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A86)^$F$51:$J$51)+$J$47*(1+C$81)/($A86-C$81)/(1+$A86)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>164.24605793886</v>
+        <v>182.859988889164</v>
       </c>
       <c r="D86" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A86)^$F$51:$J$51)+$J$47*(1+D$81)/($A86-D$81)/(1+$A86)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>172.782620736785</v>
+        <v>192.389818811176</v>
       </c>
       <c r="E86" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A86)^$F$51:$J$51)+$J$47*(1+E$81)/($A86-E$81)/(1+$A86)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>182.412990722831</v>
+        <v>203.139423493279</v>
       </c>
       <c r="F86" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A86)^$F$51:$J$51)+$J$47*(1+F$81)/($A86-F$81)/(1+$A86)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>193.36178589401</v>
+        <v>215.359003616421</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -9889,7 +10011,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -9904,27 +10026,27 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B90" s="48" t="n">
         <f aca="false">$B$34-4</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C90" s="48" t="n">
         <f aca="false">$B$34-2</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D90" s="48" t="n">
         <f aca="false">$B$34</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E90" s="48" t="n">
         <f aca="false">$B$34+2</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F90" s="48" t="n">
         <f aca="false">$B$34+4</f>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -9935,27 +10057,27 @@
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="46" t="n">
         <f aca="false">$B$30+(-0.01)</f>
-        <v>0.0930444934960543</v>
+        <v>0.0931277841927643</v>
       </c>
       <c r="B91" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A91)^$F$51:$J$51)+IS!$J$42*B$90/(1+$A91)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>212.755445745143</v>
+        <v>188.441938977644</v>
       </c>
       <c r="C91" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A91)^$F$51:$J$51)+IS!$J$42*C$90/(1+$A91)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>242.249374418605</v>
+        <v>221.595202724386</v>
       </c>
       <c r="D91" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A91)^$F$51:$J$51)+IS!$J$42*D$90/(1+$A91)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>271.743303092066</v>
+        <v>254.748466471127</v>
       </c>
       <c r="E91" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A91)^$F$51:$J$51)+IS!$J$42*E$90/(1+$A91)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>301.237231765527</v>
+        <v>287.901730217869</v>
       </c>
       <c r="F91" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A91)^$F$51:$J$51)+IS!$J$42*F$90/(1+$A91)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>330.731160438988</v>
+        <v>321.05499396461</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -9966,27 +10088,27 @@
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="46" t="n">
         <f aca="false">$B$30+(-0.005)</f>
-        <v>0.0980444934960542</v>
+        <v>0.0981277841927643</v>
       </c>
       <c r="B92" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A92)^$F$51:$J$51)+IS!$J$42*B$90/(1+$A92)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>208.773166369688</v>
+        <v>184.955087359601</v>
       </c>
       <c r="C92" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A92)^$F$51:$J$51)+IS!$J$42*C$90/(1+$A92)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>237.693739180433</v>
+        <v>217.463907043778</v>
       </c>
       <c r="D92" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A92)^$F$51:$J$51)+IS!$J$42*D$90/(1+$A92)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>266.614311991177</v>
+        <v>249.972726727956</v>
       </c>
       <c r="E92" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A92)^$F$51:$J$51)+IS!$J$42*E$90/(1+$A92)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>295.534884801921</v>
+        <v>282.481546412134</v>
       </c>
       <c r="F92" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A92)^$F$51:$J$51)+IS!$J$42*F$90/(1+$A92)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>324.455457612666</v>
+        <v>314.990366096312</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -9997,27 +10119,27 @@
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="46" t="n">
         <f aca="false">$B$30+(0)</f>
-        <v>0.103044493496054</v>
+        <v>0.103127784192764</v>
       </c>
       <c r="B93" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A93)^$F$51:$J$51)+IS!$J$42*B$90/(1+$A93)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>204.882283460997</v>
+        <v>181.547590831153</v>
       </c>
       <c r="C93" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A93)^$F$51:$J$51)+IS!$J$42*C$90/(1+$A93)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>233.24317569577</v>
+        <v>213.427336134136</v>
       </c>
       <c r="D93" s="47" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A93)^$F$51:$J$51)+IS!$J$42*D$90/(1+$A93)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>261.604067930543</v>
+        <v>245.307081437119</v>
       </c>
       <c r="E93" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A93)^$F$51:$J$51)+IS!$J$42*E$90/(1+$A93)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>289.964960165315</v>
+        <v>277.186826740102</v>
       </c>
       <c r="F93" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A93)^$F$51:$J$51)+IS!$J$42*F$90/(1+$A93)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>318.325852400088</v>
+        <v>309.066572043086</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -10028,27 +10150,27 @@
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="46" t="n">
         <f aca="false">$B$30+(0.005)</f>
-        <v>0.108044493496054</v>
+        <v>0.108127784192764</v>
       </c>
       <c r="B94" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A94)^$F$51:$J$51)+IS!$J$42*B$90/(1+$A94)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>201.080268362116</v>
+        <v>178.21726428677</v>
       </c>
       <c r="C94" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A94)^$F$51:$J$51)+IS!$J$42*C$90/(1+$A94)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>228.894769346549</v>
+        <v>209.482871139843</v>
       </c>
       <c r="D94" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A94)^$F$51:$J$51)+IS!$J$42*D$90/(1+$A94)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>256.709270330982</v>
+        <v>240.748477992915</v>
       </c>
       <c r="E94" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A94)^$F$51:$J$51)+IS!$J$42*E$90/(1+$A94)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>284.523771315414</v>
+        <v>272.014084845987</v>
       </c>
       <c r="F94" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A94)^$F$51:$J$51)+IS!$J$42*F$90/(1+$A94)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>312.338272299847</v>
+        <v>303.27969169906</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -10059,27 +10181,27 @@
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="46" t="n">
         <f aca="false">$B$30+(0.01)</f>
-        <v>0.113044493496054</v>
+        <v>0.113127784192764</v>
       </c>
       <c r="B95" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A95)^$F$51:$J$51)+IS!$J$42*B$90/(1+$A95)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>197.364673726526</v>
+        <v>174.961992664875</v>
       </c>
       <c r="C95" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A95)^$F$51:$J$51)+IS!$J$42*C$90/(1+$A95)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>224.645699390553</v>
+        <v>205.627977369428</v>
       </c>
       <c r="D95" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A95)^$F$51:$J$51)+IS!$J$42*D$90/(1+$A95)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>251.926725054579</v>
+        <v>236.29396207398</v>
       </c>
       <c r="E95" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A95)^$F$51:$J$51)+IS!$J$42*E$90/(1+$A95)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>279.207750718606</v>
+        <v>266.959946778533</v>
       </c>
       <c r="F95" s="32" t="n">
         <f aca="false">(SUMPRODUCT($F$50:$J$50,1/(1+$A95)^$F$51:$J$51)+IS!$J$42*F$90/(1+$A95)^$B$57+($B$11+$B$12+$B$13*(1-$B$14)-$B$15))/$B$9</f>
-        <v>306.488776382632</v>
+        <v>297.625931483086</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -10103,7 +10225,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -10112,7 +10234,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -10122,62 +10244,70 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="49" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="49" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="49" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49"/>
-      <c r="B8" s="50"/>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>343</v>
-      </c>
-      <c r="B9" s="50" t="s">
-        <v>344</v>
-      </c>
+      <c r="A8" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="49"/>
+      <c r="B9" s="50"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="49" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>346</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="49" t="s">
+        <v>356</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
